--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487979_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487979_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9047</v>
+        <v>5.6554</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4161</v>
+        <v>3.886</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4886</v>
+        <v>1.7694</v>
       </c>
       <c r="G2" t="n">
         <v>3.3509</v>
@@ -610,13 +610,13 @@
         <v>2.3787</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5234</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8625</v>
+        <v>-0.3927</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6609</v>
+        <v>-0.3801</v>
       </c>
       <c r="V2" t="n">
         <v>2.6808</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3771</v>
+        <v>4.5736</v>
       </c>
       <c r="E3" t="n">
         <v>0.8317</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5453</v>
+        <v>3.7419</v>
       </c>
       <c r="G3" t="n">
         <v>2.1646</v>
@@ -688,13 +688,13 @@
         <v>3.568</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6508</v>
+        <v>-0.4543</v>
       </c>
       <c r="T3" t="n">
         <v>-0.3192</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3316</v>
+        <v>-0.135</v>
       </c>
       <c r="V3" t="n">
         <v>1.2775</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. CABRERA SALMON</t>
+          <t>V. CHERNODOLIA SANZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5446</v>
+        <v>2.2614</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4775</v>
+        <v>1.3332</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0671</v>
+        <v>0.9282</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1426</v>
+        <v>0.8014</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4469</v>
+        <v>0.8661</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3043</v>
+        <v>-0.0648</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3098</v>
+        <v>2.6491</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2294</v>
+        <v>1.6615</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0804</v>
+        <v>0.9876</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1672</v>
+        <v>-1.8477</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2175</v>
+        <v>-0.7953</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3847</v>
+        <v>-1.0524</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3876</v>
+        <v>1.1893</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3787</v>
+        <v>2.1805</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1552</v>
+        <v>0.2707</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2997</v>
+        <v>-0.3247</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1444</v>
+        <v>0.5954</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1408</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1408</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. CHERNODOLIA SANZ</t>
+          <t>S. CABRERA SALMON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8405</v>
+        <v>1.4022</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6596</v>
+        <v>-0.5807</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1809</v>
+        <v>1.9828</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8014</v>
+        <v>0.1426</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8661</v>
+        <v>0.4469</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0648</v>
+        <v>-0.3043</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6491</v>
+        <v>0.3098</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6615</v>
+        <v>0.2294</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9876</v>
+        <v>0.0804</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8477</v>
+        <v>-0.1672</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7953</v>
+        <v>0.2175</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0524</v>
+        <v>-0.3847</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1805</v>
+        <v>2.3787</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1502</v>
+        <v>0.0128</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9984</v>
+        <v>0.2415</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8482</v>
+        <v>-0.2286</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.1408</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.1408</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3098</v>
+        <v>1.2922</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7909</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5189</v>
+        <v>0.6032</v>
       </c>
       <c r="G6" t="n">
         <v>0.1046</v>
@@ -922,13 +922,13 @@
         <v>0.5947</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6105</v>
+        <v>0.5929</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6902</v>
+        <v>0.5883</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.0046</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.8599</v>
       </c>
       <c r="E7" t="n">
         <v>0.0202</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.8397</v>
       </c>
       <c r="G7" t="n">
         <v>0.2918</v>
@@ -1000,13 +1000,13 @@
         <v>0.3964</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2558</v>
+        <v>0.1716</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2558</v>
+        <v>0.1716</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.7279</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5634</v>
+        <v>0.6653</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1749</v>
+        <v>0.0626</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5743</v>
@@ -1078,13 +1078,13 @@
         <v>1.9822</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3216</v>
+        <v>0.3111</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.132</v>
+        <v>-0.0302</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4536</v>
+        <v>0.3413</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. FURLAN</t>
+          <t>D. STACHOVSKIJ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4119</v>
+        <v>-0.2991</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0956</v>
+        <v>-3.6744</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5074</v>
+        <v>3.3753</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3172</v>
+        <v>-0.4824</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6107</v>
+        <v>2.0488</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.928</v>
+        <v>-2.5312</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2781</v>
+        <v>0.4709</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2781</v>
+        <v>2.227</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.7561</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5953</v>
+        <v>-0.9533</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6674</v>
+        <v>-0.1782</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.928</v>
+        <v>-0.775</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9822</v>
+        <v>-3.9645</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3876</v>
+        <v>4.3609</v>
       </c>
       <c r="S10" t="n">
-        <v>0.837</v>
+        <v>-0.4093</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8701</v>
+        <v>-0.377</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0331</v>
+        <v>-0.0323</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.337</v>
+        <v>0.1962</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0704</v>
+        <v>0.1962</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. STACHOVSKIJ</t>
+          <t>L. FURLAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8636</v>
+        <v>-0.8193</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0424</v>
+        <v>-0.3119</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1788</v>
+        <v>-0.5074</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4824</v>
+        <v>-0.3172</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0488</v>
+        <v>0.6107</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5312</v>
+        <v>-0.928</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4709</v>
+        <v>1.2781</v>
       </c>
       <c r="K11" t="n">
-        <v>2.227</v>
+        <v>1.2781</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.7561</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9533</v>
+        <v>-1.5953</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1782</v>
+        <v>-0.6674</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.775</v>
+        <v>-0.928</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3964</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9645</v>
+        <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
-        <v>4.3609</v>
+        <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9738</v>
+        <v>0.4295</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.745</v>
+        <v>0.4626</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2289</v>
+        <v>-0.0331</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1962</v>
+        <v>-0.337</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1962</v>
+        <v>-0.0704</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5099</v>
+        <v>-1.6222</v>
       </c>
       <c r="E12" t="n">
         <v>-1.0757</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4342</v>
+        <v>-0.5465</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6935</v>
@@ -1390,13 +1390,13 @@
         <v>0.1982</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0235</v>
+        <v>-0.1358</v>
       </c>
       <c r="T12" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1013</v>
+        <v>-0.011</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. COCA LOPEZ</t>
+          <t>J. LOPEZ MUNOZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.9997</v>
+        <v>-3.2505</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4077</v>
+        <v>-2.0504</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5919</v>
+        <v>-1.2002</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.4547</v>
+        <v>-2.5604</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7869</v>
+        <v>-0.9149</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6677</v>
+        <v>-1.6455</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0202</v>
+        <v>0.2285</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0202</v>
+        <v>0.1482</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.0804</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4748</v>
+        <v>-2.7889</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8071</v>
+        <v>-1.0631</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6677</v>
+        <v>-1.7258</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.9822</v>
+        <v>1.3876</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.3787</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4372</v>
+        <v>-0.8002</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5543</v>
+        <v>-0.6138</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1171</v>
+        <v>-0.1864</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-1.2775</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUNOZ</t>
+          <t>J. COCA LOPEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.6819</v>
+        <v>-3.2772</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.6221</v>
+        <v>-1.7133</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0598</v>
+        <v>-1.5639</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.5604</v>
+        <v>-1.4547</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9149</v>
+        <v>-0.7869</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.6455</v>
+        <v>-0.6677</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2285</v>
+        <v>0.0202</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1482</v>
+        <v>0.0202</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0804</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.7889</v>
+        <v>-1.4748</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0631</v>
+        <v>-0.8071</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7258</v>
+        <v>-0.6677</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3876</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3787</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2316</v>
+        <v>0.1597</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1855</v>
+        <v>0.2487</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.046</v>
+        <v>-0.089</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2775</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,16 +1579,16 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.7949</v>
+        <v>8.107000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.6902</v>
+        <v>-1.3783</v>
       </c>
       <c r="F15" t="n">
-        <v>9.485099999999996</v>
+        <v>9.485099999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>1.376100000000001</v>
+        <v>1.3761</v>
       </c>
       <c r="H15" t="n">
         <v>2.6771</v>
@@ -1609,7 +1609,7 @@
         <v>-12.1404</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.926699999999999</v>
+        <v>-4.9267</v>
       </c>
       <c r="O15" t="n">
         <v>-7.213800000000001</v>
@@ -1624,13 +1624,13 @@
         <v>21.8046</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9360000000000002</v>
+        <v>-0.6240000000000003</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9530999999999998</v>
+        <v>-0.6412999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01719999999999997</v>
+        <v>0.01739999999999994</v>
       </c>
       <c r="V15" t="n">
         <v>2.3992</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.7388</v>
+        <v>4.5736</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7858</v>
+        <v>3.4802</v>
       </c>
       <c r="F16" t="n">
-        <v>0.953</v>
+        <v>1.0934</v>
       </c>
       <c r="G16" t="n">
         <v>3.3141</v>
@@ -1702,13 +1702,13 @@
         <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3652</v>
+        <v>0.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3599</v>
+        <v>0.0543</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0053</v>
+        <v>0.1457</v>
       </c>
       <c r="V16" t="n">
         <v>0.2666</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1163</v>
+        <v>1.9687</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9677</v>
+        <v>0.7639</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1487</v>
+        <v>1.2048</v>
       </c>
       <c r="G17" t="n">
         <v>1.3264</v>
@@ -1780,13 +1780,13 @@
         <v>1.1893</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1843</v>
+        <v>0.0367</v>
       </c>
       <c r="T17" t="n">
-        <v>0.18</v>
+        <v>-0.0238</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0043</v>
+        <v>0.0605</v>
       </c>
       <c r="V17" t="n">
         <v>0.4074</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6077</v>
+        <v>1.8114</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1327</v>
+        <v>2.3364</v>
       </c>
       <c r="F18" t="n">
         <v>-0.525</v>
@@ -1858,10 +1858,10 @@
         <v>1.3876</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4809</v>
+        <v>-0.2772</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5616</v>
+        <v>-0.3578</v>
       </c>
       <c r="U18" t="n">
         <v>0.08069999999999999</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8064</v>
+        <v>1.0101</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6384</v>
+        <v>0.8421</v>
       </c>
       <c r="F19" t="n">
         <v>0.168</v>
@@ -1936,10 +1936,10 @@
         <v>1.1893</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1982</v>
+        <v>0.0055</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3744</v>
+        <v>-0.1706</v>
       </c>
       <c r="U19" t="n">
         <v>0.1762</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. MARTINEZ GUZMAN</t>
+          <t>J. PEREZ CABELLO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4332</v>
+        <v>-0.8891</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1824</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7492</v>
+        <v>-0.8138</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6974</v>
+        <v>0.9978</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9685</v>
+        <v>-1.036</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7289</v>
+        <v>2.0338</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2375</v>
+        <v>1.9931</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6388</v>
+        <v>0.1009</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5988</v>
+        <v>1.8922</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4599</v>
+        <v>-0.9953</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3298</v>
+        <v>-1.1369</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1301</v>
+        <v>0.1415</v>
       </c>
       <c r="P23" t="n">
         <v>-0.3964</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5947</v>
+        <v>1.5858</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3237</v>
+        <v>-0.6204</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0463</v>
+        <v>-0.0862</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2774</v>
+        <v>-0.5342</v>
       </c>
       <c r="V23" t="n">
-        <v>0.337</v>
+        <v>-0.8701</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.337</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. PEREZ CABELLO</t>
+          <t>J. MARTINEZ GUZMAN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.9897</v>
+        <v>-1.1567</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1285</v>
+        <v>-1.7936</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1181</v>
+        <v>0.6369</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9978</v>
+        <v>-1.6974</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.036</v>
+        <v>-0.9685</v>
       </c>
       <c r="I24" t="n">
-        <v>2.0338</v>
+        <v>-0.7289</v>
       </c>
       <c r="J24" t="n">
-        <v>1.9931</v>
+        <v>-1.2375</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1009</v>
+        <v>-0.6388</v>
       </c>
       <c r="L24" t="n">
-        <v>1.8922</v>
+        <v>-0.5988</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9953</v>
+        <v>-0.4599</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1369</v>
+        <v>-0.3298</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1415</v>
+        <v>-0.1301</v>
       </c>
       <c r="P24" t="n">
         <v>-0.3964</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5858</v>
+        <v>0.5947</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7209</v>
+        <v>0.6002</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1176</v>
+        <v>0.4351</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8385</v>
+        <v>0.1651</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.8701</v>
+        <v>0.337</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.8701</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.2277</v>
+        <v>-1.3403</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.763</v>
+        <v>-1.1518</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4647</v>
+        <v>-0.1885</v>
       </c>
       <c r="G25" t="n">
         <v>-1.25</v>
@@ -2404,13 +2404,13 @@
         <v>2.5769</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3652</v>
+        <v>0.5222</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5064</v>
+        <v>0.1048</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1412</v>
+        <v>0.4174</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2071</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. ESPINAL REYNOSO</t>
+          <t>S. OKUNGHAE FRANCIS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.565</v>
+        <v>-2.6703</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.4044</v>
+        <v>-2.2243</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8394</v>
+        <v>-0.4461</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.4547</v>
+        <v>-2.2436</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.3751</v>
+        <v>-1.5606</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.0796</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.3453</v>
+        <v>-1.0561</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.188</v>
+        <v>-0.4975</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.1574</v>
+        <v>-0.5586</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.1094</v>
+        <v>-1.1875</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.1871</v>
+        <v>-1.0631</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.9223</v>
+        <v>-0.1244</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R26" t="n">
-        <v>2.1805</v>
+        <v>1.5858</v>
       </c>
       <c r="S26" t="n">
-        <v>1.6122</v>
+        <v>-0.4882</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9142</v>
+        <v>-0.177</v>
       </c>
       <c r="U26" t="n">
-        <v>0.698</v>
+        <v>-0.3112</v>
       </c>
       <c r="V26" t="n">
-        <v>0.0704</v>
+        <v>-0.5331</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0704</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S. OKUNGHAE FRANCIS</t>
+          <t>J. ESPINAL REYNOSO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.512</v>
+        <v>-3.3669</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.7336</v>
+        <v>-4.1175</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.7784</v>
+        <v>0.7506</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.2436</v>
+        <v>-3.4547</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.5606</v>
+        <v>-1.3751</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-2.0796</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.0561</v>
+        <v>-1.3453</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.4975</v>
+        <v>-0.188</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.5586</v>
+        <v>-1.1574</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.1875</v>
+        <v>-2.1094</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.0631</v>
+        <v>-1.1871</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.1244</v>
+        <v>-0.9223</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5947</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5858</v>
+        <v>2.1805</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.33</v>
+        <v>0.8103</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.6864</v>
+        <v>0.2012</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.6435999999999999</v>
+        <v>0.6091</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.5331</v>
+        <v>0.0704</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.5331</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-7.9092</v>
+        <v>-7.629</v>
       </c>
       <c r="E28" t="n">
-        <v>-8.897500000000001</v>
+        <v>-8.388199999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9883</v>
+        <v>0.7591</v>
       </c>
       <c r="G28" t="n">
         <v>-1.6411</v>
@@ -2638,13 +2638,13 @@
         <v>2.5769</v>
       </c>
       <c r="S28" t="n">
-        <v>0.6081</v>
+        <v>0.8883</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.444</v>
+        <v>0.0653</v>
       </c>
       <c r="U28" t="n">
-        <v>1.0522</v>
+        <v>0.823</v>
       </c>
       <c r="V28" t="n">
         <v>-0.5331</v>
@@ -2671,16 +2671,16 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-7.794700000000001</v>
+        <v>-7.115600000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-9.4848</v>
+        <v>-9.485099999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>1.6903</v>
+        <v>2.3693</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.375900000000001</v>
+        <v>-1.3759</v>
       </c>
       <c r="H29" t="n">
         <v>-2.677300000000001</v>
@@ -2692,19 +2692,19 @@
         <v>12.1408</v>
       </c>
       <c r="K29" t="n">
-        <v>4.926700000000001</v>
+        <v>4.926700000000002</v>
       </c>
       <c r="L29" t="n">
-        <v>7.213699999999999</v>
+        <v>7.213700000000001</v>
       </c>
       <c r="M29" t="n">
         <v>-13.5166</v>
       </c>
       <c r="N29" t="n">
-        <v>-7.603999999999999</v>
+        <v>-7.604000000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>-5.912699999999999</v>
+        <v>-5.9127</v>
       </c>
       <c r="P29" t="n">
         <v>-4.955499999999999</v>
@@ -2716,13 +2716,13 @@
         <v>16.849</v>
       </c>
       <c r="S29" t="n">
-        <v>0.9358999999999998</v>
+        <v>1.615</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.01719999999999983</v>
+        <v>-0.01710000000000009</v>
       </c>
       <c r="U29" t="n">
-        <v>0.9532</v>
+        <v>1.6323</v>
       </c>
       <c r="V29" t="n">
         <v>-2.399</v>
@@ -2731,7 +2731,7 @@
         <v>0.1962</v>
       </c>
       <c r="X29" t="n">
-        <v>-2.5952</v>
+        <v>-2.595200000000001</v>
       </c>
     </row>
   </sheetData>
